--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-prelevement.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-prelevement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-prelevement.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-prelevement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6095,7 +6095,7 @@
         <v>180</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>75</v>
